--- a/output/pdf_financials_xlsx/LUN.xlsx
+++ b/output/pdf_financials_xlsx/LUN.xlsx
@@ -1047,10 +1047,10 @@
         <v>1.945</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>3.527</v>
+        <v>1.857</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>4.496</v>
@@ -2037,10 +2037,10 @@
         <v>129.019</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>51.118</v>
+        <v>52.788</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-280.16</v>
+        <v>-280.724</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>123.683</v>
@@ -2155,10 +2155,10 @@
         <v>277.168</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>259.821</v>
+        <v>261.491</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>274.861</v>
+        <v>274.297</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>558.55</v>
@@ -2215,10 +2215,10 @@
         <v>38.0839317268083</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>27.31180241224244</v>
+        <v>27.48734907717115</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>16.14979784916922</v>
+        <v>16.11665933192984</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>36.13827979070789</v>
@@ -4029,10 +4029,10 @@
         <v>67.09</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>19.1</v>
+        <v>18.382</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>75.5</v>
+        <v>6613.7</v>
       </c>
     </row>
     <row r="62">
@@ -7681,10 +7681,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-1.348</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-553.029</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>-445</v>
@@ -7739,10 +7739,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-1.348</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-553.029</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>-445</v>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -56752,7 +56752,11 @@
           <t>Debt and finance lease payments</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -76361,7 +76365,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -79027,7 +79031,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -84457,7 +84461,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -87025,7 +87029,7 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -89116,7 +89120,7 @@
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -91090,7 +91094,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
@@ -94777,7 +94781,7 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">

--- a/output/pdf_financials_xlsx/LUN.xlsx
+++ b/output/pdf_financials_xlsx/LUN.xlsx
@@ -1306,12 +1306,10 @@
         <v>531.848</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>153.354</v>
-      </c>
-      <c r="R16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-61.3</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>1653.5</v>
       </c>
     </row>
     <row r="17">
@@ -1645,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-754.096</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>55.066</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1782,12 +1780,10 @@
         <v>315.249</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>153.354</v>
-      </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-61.3</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1653.5</v>
       </c>
     </row>
     <row r="24">
@@ -2064,12 +2060,10 @@
         <v>520.711</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>137.254</v>
-      </c>
-      <c r="R27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-77.40000000000001</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>1638.9</v>
       </c>
     </row>
     <row r="28">
@@ -2182,12 +2176,10 @@
         <v>1174.307</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>711.454</v>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>496.8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>2257.8</v>
       </c>
     </row>
     <row r="30">
@@ -2242,12 +2234,10 @@
         <v>34.61911389393578</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>21.75633772667503</v>
-      </c>
-      <c r="R30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.19219595731017</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>55.70413500444094</v>
       </c>
     </row>
     <row r="31">
@@ -2302,12 +2292,10 @@
         <v>40.72573366826612</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2362,12 +2350,10 @@
         <v>9.293686434594498</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>4.689581358368246</v>
-      </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.874560410996606</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>40.79492746471923</v>
       </c>
     </row>
     <row r="33">
@@ -2744,43 +2730,43 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>12.607</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>9.246</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>11.085</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>12.593</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>17.111</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>27.356</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>19.556</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>39.378</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>31.869</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>26.649</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>56.16</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
@@ -2802,43 +2788,43 @@
         <v>120.066</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>110.808</v>
+        <v>123.415</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>114.196</v>
+        <v>123.442</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>404.967</v>
+        <v>416.052</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>192.194</v>
+        <v>204.787</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>338.931</v>
+        <v>356.042</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>425.671</v>
+        <v>453.027</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>384.332</v>
+        <v>403.888</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>384.332</v>
+        <v>423.71</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>602.674</v>
+        <v>634.543</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>576.178</v>
+        <v>602.827</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>828.871</v>
+        <v>885.0309999999999</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>510.9</v>
+        <v>578.4</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>824.6</v>
+        <v>884.6</v>
       </c>
     </row>
     <row r="42">
@@ -3208,13 +3194,13 @@
         <v>6.869</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.494</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>24.909</v>
+        <v>15.663</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>49.241</v>
+        <v>38.156</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>5.101</v>
@@ -6244,10 +6230,8 @@
       <c r="Q99" s="3" t="n">
         <v>153.354</v>
       </c>
-      <c r="R99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R99" s="3" t="n">
+        <v>1653.5</v>
       </c>
     </row>
     <row r="100">
@@ -7096,10 +7080,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-28.654</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>52.614</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
@@ -7114,10 +7098,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-41.7</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="115">
@@ -7133,19 +7117,19 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>52.28</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>7.972</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>-18.379</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>4.302</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -7935,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0</v>
+        <v>-1.731</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-6.419</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
@@ -42697,7 +42681,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -44294,7 +44282,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -47949,7 +47941,11 @@
           <t>Purchase of marketable securities (Note 8)</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -49525,7 +49521,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -54968,7 +54968,11 @@
           <t>Proceeds from sale (purchase) of marketable securities</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -58954,7 +58958,11 @@
           <t>Proceeds from sale of marketable securities, net</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
@@ -60550,7 +60558,11 @@
           <t>Proceeds from sale of marketable securities, net</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -62043,7 +62055,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -63524,7 +63540,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -65619,7 +65639,11 @@
           <t>(Acquisition of) proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
           <t>-</t>
@@ -66918,7 +66942,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -70908,7 +70936,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E637" s="5" t="n">
         <v>-957.061</v>
       </c>
@@ -71700,7 +71732,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E645" s="5" t="n">
         <v>-134.122</v>
       </c>
@@ -75175,7 +75211,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E680" t="inlineStr">
         <is>
           <t>-</t>
@@ -75765,7 +75805,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
           <t>-</t>
@@ -83661,7 +83705,11 @@
           <t>Gain (loss) from discontinued operations (Note 9)</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E768" t="inlineStr">
         <is>
           <t>-</t>
@@ -83756,7 +83804,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E769" t="inlineStr">
         <is>
           <t>-</t>
@@ -84061,7 +84113,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E772" t="inlineStr">
         <is>
           <t>-</t>
@@ -98113,7 +98169,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E914" s="5" t="n">
         <v>160.13</v>
       </c>
